--- a/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -65,6 +65,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
   </si>
 </sst>
 </file>
@@ -614,7 +632,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -644,6 +662,52 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920236</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920228</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
@@ -480,19 +480,19 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>32</v>
       </c>
       <c r="G2">
-        <v>86.48999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="H2">
         <v>7.4</v>
@@ -545,13 +545,13 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -607,19 +607,19 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>32</v>
       </c>
       <c r="G2">
-        <v>86.48999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="H2">
         <v>7.4</v>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -67,22 +67,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
   </si>
   <si>
     <t>ACEVEDO</t>
   </si>
   <si>
-    <t>GALEOTE</t>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>JENIFER</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
   </si>
   <si>
     <t>GENARO RAFAEL</t>
   </si>
   <si>
-    <t>GERMAN ISAI</t>
+    <t>VICTOR GAMALIEL</t>
   </si>
 </sst>
 </file>
@@ -548,16 +584,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -613,16 +652,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>88.89</v>
+        <v>77.78</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -632,7 +671,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -664,16 +703,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920236</v>
+        <v>20330051920237</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -687,24 +726,116 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920228</v>
+        <v>20330051920225</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920375</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920228</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920236</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920244</v>
+      </c>
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
@@ -67,55 +67,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>MARIANO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
     <t>LORENZO</t>
   </si>
   <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>JENIFER</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
     <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>JUAN ALBERTO</t>
-  </si>
-  <si>
-    <t>JENIFER</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
   </si>
   <si>
     <t>VICTOR GAMALIEL</t>
@@ -703,7 +703,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920237</v>
+        <v>20330051920225</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -721,12 +721,12 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920225</v>
+        <v>20330051920375</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -749,7 +749,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920375</v>
+        <v>20330051920228</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920228</v>
+        <v>20330051920236</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920236</v>
+        <v>20330051920237</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -67,58 +67,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>JUAN ALBERTO</t>
-  </si>
-  <si>
-    <t>JENIFER</t>
-  </si>
-  <si>
     <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
   </si>
 </sst>
 </file>
@@ -584,7 +539,7 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>9</v>
@@ -596,7 +551,7 @@
         <v>75</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -652,16 +607,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>77.78</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -671,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -703,16 +658,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920225</v>
+        <v>20330051920228</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -721,121 +676,6 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920375</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920228</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920236</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920237</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920244</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>
